--- a/data/trans_bre/P20-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P20-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,22</t>
+          <t>-2,09; 4,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 9,32</t>
+          <t>-1,44; 9,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,29</t>
+          <t>1,86; 11,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,65</t>
+          <t>-0,49; 5,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 222,01</t>
+          <t>-45,98; 239,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 161,33</t>
+          <t>-13,58; 156,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,67; 304,41</t>
+          <t>17,44; 313,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 233,06</t>
+          <t>-11,28; 224,23</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 7,43</t>
+          <t>0,7; 7,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 6,78</t>
+          <t>-1,28; 6,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,96</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,75; -0,4</t>
+          <t>-6,56; -0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 192,6</t>
+          <t>8,71; 191,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 104,63</t>
+          <t>-13,66; 105,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 205,21</t>
+          <t>-6,52; 177,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-68,25; -5,1</t>
+          <t>-65,35; 0,83</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,5</t>
+          <t>-0,5; 5,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,31</t>
+          <t>-1,41; 7,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,38</t>
+          <t>3,81; 11,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 4,91</t>
+          <t>-3,34; 4,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 534,58</t>
+          <t>-22,98; 575,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 134,27</t>
+          <t>-18,25; 136,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,38; 607,68</t>
+          <t>72,7; 703,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 75,31</t>
+          <t>-32,24; 68,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,16</t>
+          <t>0,89; 6,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 8,41</t>
+          <t>0,92; 8,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,7</t>
+          <t>-3,35; 5,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,15</t>
+          <t>-5,73; 4,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,54; 616,13</t>
+          <t>10,77; 529,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 221,48</t>
+          <t>12,11; 216,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,75; 79,53</t>
+          <t>-35,17; 96,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 74,16</t>
+          <t>-56,09; 80,5</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,23</t>
+          <t>-2,88; 7,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 8,84</t>
+          <t>-1,53; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 5,42</t>
+          <t>-2,69; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,13</t>
+          <t>-1,05; 3,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 219,91</t>
+          <t>-33,62; 189,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 215,93</t>
+          <t>-20,35; 216,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 239,67</t>
+          <t>-52,13; 249,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 331,06</t>
+          <t>-30,77; 292,25</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,99; 11,91</t>
+          <t>2,82; 11,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,69</t>
+          <t>-0,8; 8,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 8,91</t>
+          <t>-1,8; 8,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,45</t>
+          <t>-4,56; 3,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,45; 514,2</t>
+          <t>41,97; 465,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 235,33</t>
+          <t>-9,85; 279,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 169,2</t>
+          <t>-22,28; 164,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,83; 50,88</t>
+          <t>-42,3; 44,51</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,49</t>
+          <t>-0,54; 5,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,41; 6,95</t>
+          <t>1,23; 6,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,93</t>
+          <t>0,25; 5,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,15</t>
+          <t>-3,94; 3,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 124,3</t>
+          <t>-8,09; 119,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,3; 199,52</t>
+          <t>16,81; 203,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 234,99</t>
+          <t>-0,06; 199,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-56,22; 61,24</t>
+          <t>-55,84; 63,56</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,34</t>
+          <t>0,63; 5,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,0</t>
+          <t>0,16; 5,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 3,85</t>
+          <t>-0,86; 3,83</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,79</t>
+          <t>-0,24; 3,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,05; 224,07</t>
+          <t>12,48; 204,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,12; 138,63</t>
+          <t>-0,76; 126,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,11; 114,39</t>
+          <t>-16,54; 106,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 290,09</t>
+          <t>-6,45; 285,89</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,51</t>
+          <t>2,26; 4,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,7</t>
+          <t>2,15; 4,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,06</t>
+          <t>1,82; 4,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,87</t>
+          <t>-0,91; 2,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44,27; 120,95</t>
+          <t>45,69; 120,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,09; 87,22</t>
+          <t>32,05; 84,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,15; 95,6</t>
+          <t>33,56; 97,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 41,27</t>
+          <t>-14,87; 46,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P20-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,66</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,86</t>
+          <t>-2,41; 4,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 9,68</t>
+          <t>-1,56; 9,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 11,12</t>
+          <t>2,0; 11,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,35</t>
+          <t>0,44; 6,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,98; 239,92</t>
+          <t>-53,97; 217,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 156,69</t>
+          <t>-16,34; 141,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,44; 313,76</t>
+          <t>17,46; 308,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 224,23</t>
+          <t>3,15; 263,24</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,12</t>
+          <t>-3,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-41,77%</t>
+          <t>-42,14%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 7,38</t>
+          <t>0,68; 7,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,85</t>
+          <t>-0,77; 6,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,69</t>
+          <t>-0,13; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; -0,31</t>
+          <t>-6,27; -0,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 191,72</t>
+          <t>9,21; 196,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 105,2</t>
+          <t>-7,72; 106,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 177,83</t>
+          <t>-2,71; 199,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 0,83</t>
+          <t>-64,1; -1,21</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 5,53</t>
+          <t>-0,44; 5,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 7,63</t>
+          <t>-1,54; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 11,23</t>
+          <t>3,67; 10,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 4,43</t>
+          <t>-3,06; 4,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 575,54</t>
+          <t>-23,88; 489,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 136,5</t>
+          <t>-18,62; 138,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,7; 703,98</t>
+          <t>79,95; 670,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 68,26</t>
+          <t>-29,99; 72,62</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,89%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,36</t>
+          <t>0,4; 5,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,79</t>
+          <t>0,73; 8,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 5,02</t>
+          <t>-3,65; 4,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 4,02</t>
+          <t>-3,19; 6,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 529,47</t>
+          <t>3,54; 479,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,11; 216,81</t>
+          <t>9,02; 218,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,17; 96,29</t>
+          <t>-36,85; 88,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,09; 80,5</t>
+          <t>-32,08; 126,3</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 7,81</t>
+          <t>-2,63; 8,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 8,66</t>
+          <t>-2,1; 8,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 5,22</t>
+          <t>-2,67; 5,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 3,72</t>
+          <t>-0,65; 3,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-33,62; 189,82</t>
+          <t>-33,61; 201,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 216,99</t>
+          <t>-27,52; 218,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-52,13; 249,29</t>
+          <t>-52,0; 242,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,77; 292,25</t>
+          <t>-25,77; 296,54</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-6,67%</t>
+          <t>-5,65%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,57</t>
+          <t>3,08; 11,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 8,67</t>
+          <t>-0,69; 8,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 8,17</t>
+          <t>-2,22; 8,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 3,07</t>
+          <t>-4,48; 3,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>41,97; 465,15</t>
+          <t>46,09; 490,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 279,33</t>
+          <t>-11,6; 241,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 164,94</t>
+          <t>-24,09; 159,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 44,51</t>
+          <t>-41,47; 46,82</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,33</t>
+          <t>-0,21; 5,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,79</t>
+          <t>1,17; 6,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,88</t>
+          <t>0,42; 5,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,2</t>
+          <t>-0,49; 4,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 119,13</t>
+          <t>-4,61; 126,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,81; 203,64</t>
+          <t>18,64; 194,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 199,69</t>
+          <t>8,37; 209,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 63,56</t>
+          <t>-6,81; 101,42</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,15</t>
+          <t>0,75; 5,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,01</t>
+          <t>0,1; 4,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,83</t>
+          <t>-0,86; 3,71</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 3,89</t>
+          <t>-1,17; 2,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,48; 204,5</t>
+          <t>14,69; 202,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 126,33</t>
+          <t>-0,34; 137,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 106,71</t>
+          <t>-16,41; 102,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 285,89</t>
+          <t>-28,42; 103,55</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,46</t>
+          <t>2,04; 4,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,76</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,23</t>
+          <t>1,66; 4,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,02</t>
+          <t>-0,26; 1,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>45,69; 120,31</t>
+          <t>44,22; 120,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,05; 84,73</t>
+          <t>31,37; 87,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,56; 97,41</t>
+          <t>30,11; 93,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 46,87</t>
+          <t>-4,07; 34,6</t>
         </is>
       </c>
     </row>
